--- a/연구코드/data/신촌/landmark/신촌_landmarks.xlsx
+++ b/연구코드/data/신촌/landmark/신촌_landmarks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="77">
   <si>
     <t>PatientID</t>
   </si>
@@ -217,6 +217,9 @@
     <t>Pre 3mm</t>
   </si>
   <si>
+    <t>Pre 2mm</t>
+  </si>
+  <si>
     <t>iCT 256</t>
   </si>
   <si>
@@ -232,7 +235,16 @@
     <t>SOMATOM Definition AS+</t>
   </si>
   <si>
+    <t>SOMATOM Definition Flash</t>
+  </si>
+  <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>missing</t>
   </si>
 </sst>
 </file>
@@ -590,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BK7"/>
+  <dimension ref="A1:BK8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:63">
@@ -792,13 +804,13 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2">
         <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -807,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>17</v>
@@ -819,7 +831,7 @@
         <v>1000.84</v>
       </c>
       <c r="L2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2">
         <v>37</v>
@@ -831,7 +843,7 @@
         <v>1060.84</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q2">
         <v>72</v>
@@ -843,7 +855,7 @@
         <v>1165.84</v>
       </c>
       <c r="T2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U2">
         <v>80</v>
@@ -855,7 +867,7 @@
         <v>1189.84</v>
       </c>
       <c r="X2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y2">
         <v>89</v>
@@ -867,7 +879,7 @@
         <v>1216.84</v>
       </c>
       <c r="AB2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC2">
         <v>99</v>
@@ -879,7 +891,7 @@
         <v>1246.84</v>
       </c>
       <c r="AF2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG2">
         <v>109</v>
@@ -891,7 +903,7 @@
         <v>1276.84</v>
       </c>
       <c r="AJ2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK2">
         <v>119</v>
@@ -903,7 +915,7 @@
         <v>1306.84</v>
       </c>
       <c r="AN2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO2">
         <v>128</v>
@@ -915,7 +927,7 @@
         <v>1333.84</v>
       </c>
       <c r="AR2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS2">
         <v>136</v>
@@ -927,7 +939,7 @@
         <v>1357.84</v>
       </c>
       <c r="AV2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW2">
         <v>144</v>
@@ -939,7 +951,7 @@
         <v>1381.84</v>
       </c>
       <c r="AZ2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BA2">
         <v>151</v>
@@ -951,7 +963,7 @@
         <v>1402.84</v>
       </c>
       <c r="BD2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE2">
         <v>164</v>
@@ -963,7 +975,7 @@
         <v>1441.84</v>
       </c>
       <c r="BH2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BI2">
         <v>158</v>
@@ -983,13 +995,13 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3">
         <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -998,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3">
         <v>15</v>
@@ -1010,7 +1022,7 @@
         <v>-420</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3">
         <v>45</v>
@@ -1022,7 +1034,7 @@
         <v>-345</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q3">
         <v>83</v>
@@ -1034,7 +1046,7 @@
         <v>-250</v>
       </c>
       <c r="T3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U3">
         <v>96</v>
@@ -1046,7 +1058,7 @@
         <v>-217.5</v>
       </c>
       <c r="X3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y3">
         <v>110</v>
@@ -1058,7 +1070,7 @@
         <v>-182.5</v>
       </c>
       <c r="AB3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC3">
         <v>125</v>
@@ -1070,7 +1082,7 @@
         <v>-145</v>
       </c>
       <c r="AF3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG3">
         <v>139</v>
@@ -1082,7 +1094,7 @@
         <v>-110</v>
       </c>
       <c r="AJ3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK3">
         <v>154</v>
@@ -1094,7 +1106,7 @@
         <v>-72.5</v>
       </c>
       <c r="AN3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO3">
         <v>167</v>
@@ -1106,7 +1118,7 @@
         <v>-40</v>
       </c>
       <c r="AR3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS3">
         <v>178</v>
@@ -1118,7 +1130,7 @@
         <v>-12.5</v>
       </c>
       <c r="AV3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW3">
         <v>189</v>
@@ -1130,7 +1142,7 @@
         <v>15</v>
       </c>
       <c r="AZ3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BA3">
         <v>200</v>
@@ -1142,7 +1154,7 @@
         <v>42.5</v>
       </c>
       <c r="BD3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE3">
         <v>219</v>
@@ -1154,7 +1166,7 @@
         <v>90</v>
       </c>
       <c r="BH3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BI3">
         <v>210</v>
@@ -1174,13 +1186,13 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4">
         <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -1189,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -1201,7 +1213,7 @@
         <v>-391.187</v>
       </c>
       <c r="L4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4">
         <v>31</v>
@@ -1213,7 +1225,7 @@
         <v>-334.187</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q4">
         <v>59</v>
@@ -1225,7 +1237,7 @@
         <v>-250.187</v>
       </c>
       <c r="T4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U4">
         <v>68</v>
@@ -1237,7 +1249,7 @@
         <v>-223.187</v>
       </c>
       <c r="X4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y4">
         <v>78</v>
@@ -1249,7 +1261,7 @@
         <v>-193.187</v>
       </c>
       <c r="AB4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC4">
         <v>89</v>
@@ -1261,7 +1273,7 @@
         <v>-160.187</v>
       </c>
       <c r="AF4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG4">
         <v>100</v>
@@ -1273,7 +1285,7 @@
         <v>-127.187</v>
       </c>
       <c r="AJ4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK4">
         <v>111</v>
@@ -1285,7 +1297,7 @@
         <v>-94.187</v>
       </c>
       <c r="AN4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO4">
         <v>121</v>
@@ -1297,7 +1309,7 @@
         <v>-64.187</v>
       </c>
       <c r="AR4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS4">
         <v>130</v>
@@ -1309,7 +1321,7 @@
         <v>-37.187</v>
       </c>
       <c r="AV4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW4">
         <v>138</v>
@@ -1321,7 +1333,7 @@
         <v>-13.187</v>
       </c>
       <c r="AZ4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BA4">
         <v>146</v>
@@ -1333,7 +1345,7 @@
         <v>10.812</v>
       </c>
       <c r="BD4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE4">
         <v>161</v>
@@ -1345,7 +1357,7 @@
         <v>55.812</v>
       </c>
       <c r="BH4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BI4">
         <v>154</v>
@@ -1365,13 +1377,13 @@
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1380,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>13</v>
@@ -1392,7 +1404,7 @@
         <v>-605.25</v>
       </c>
       <c r="L5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5">
         <v>36</v>
@@ -1404,7 +1416,7 @@
         <v>-536.25</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q5">
         <v>68</v>
@@ -1416,7 +1428,7 @@
         <v>-440.25</v>
       </c>
       <c r="T5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U5">
         <v>78</v>
@@ -1428,7 +1440,7 @@
         <v>-410.25</v>
       </c>
       <c r="X5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y5">
         <v>88</v>
@@ -1440,7 +1452,7 @@
         <v>-380.25</v>
       </c>
       <c r="AB5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC5">
         <v>99</v>
@@ -1452,7 +1464,7 @@
         <v>-347.25</v>
       </c>
       <c r="AF5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG5">
         <v>110</v>
@@ -1464,7 +1476,7 @@
         <v>-314.25</v>
       </c>
       <c r="AJ5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK5">
         <v>120</v>
@@ -1476,7 +1488,7 @@
         <v>-284.25</v>
       </c>
       <c r="AN5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO5">
         <v>131</v>
@@ -1488,7 +1500,7 @@
         <v>-251.25</v>
       </c>
       <c r="AR5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS5">
         <v>141</v>
@@ -1500,7 +1512,7 @@
         <v>-221.25</v>
       </c>
       <c r="AV5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW5">
         <v>150</v>
@@ -1512,7 +1524,7 @@
         <v>-194.25</v>
       </c>
       <c r="AZ5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BA5">
         <v>159</v>
@@ -1524,7 +1536,7 @@
         <v>-167.25</v>
       </c>
       <c r="BD5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE5">
         <v>150</v>
@@ -1536,7 +1548,7 @@
         <v>-194.25</v>
       </c>
       <c r="BH5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BI5">
         <v>167</v>
@@ -1556,13 +1568,13 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <v>220</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -1571,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -1583,7 +1595,7 @@
         <v>-485.75</v>
       </c>
       <c r="L6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6">
         <v>40</v>
@@ -1595,7 +1607,7 @@
         <v>-415.75</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q6">
         <v>79</v>
@@ -1607,7 +1619,7 @@
         <v>-318.25</v>
       </c>
       <c r="T6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U6">
         <v>91</v>
@@ -1619,7 +1631,7 @@
         <v>-288.25</v>
       </c>
       <c r="X6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y6">
         <v>102</v>
@@ -1631,7 +1643,7 @@
         <v>-260.75</v>
       </c>
       <c r="AB6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC6">
         <v>116</v>
@@ -1643,7 +1655,7 @@
         <v>-225.75</v>
       </c>
       <c r="AF6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG6">
         <v>130</v>
@@ -1655,7 +1667,7 @@
         <v>-190.75</v>
       </c>
       <c r="AJ6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK6">
         <v>144</v>
@@ -1667,7 +1679,7 @@
         <v>-155.75</v>
       </c>
       <c r="AN6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO6">
         <v>158</v>
@@ -1679,7 +1691,7 @@
         <v>-120.75</v>
       </c>
       <c r="AR6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS6">
         <v>171</v>
@@ -1691,7 +1703,7 @@
         <v>-88.25</v>
       </c>
       <c r="AV6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW6">
         <v>183</v>
@@ -1703,7 +1715,7 @@
         <v>-58.25</v>
       </c>
       <c r="AZ6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BA6">
         <v>194</v>
@@ -1715,7 +1727,7 @@
         <v>-30.75</v>
       </c>
       <c r="BD6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE6">
         <v>201</v>
@@ -1727,7 +1739,7 @@
         <v>-13.25</v>
       </c>
       <c r="BH6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BI6">
         <v>205</v>
@@ -1747,13 +1759,13 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -1762,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1774,7 +1786,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="L7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7">
         <v>31</v>
@@ -1786,7 +1798,7 @@
         <v>150.4</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>61</v>
@@ -1798,7 +1810,7 @@
         <v>240.4</v>
       </c>
       <c r="T7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U7">
         <v>70</v>
@@ -1810,7 +1822,7 @@
         <v>267.4</v>
       </c>
       <c r="X7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y7">
         <v>79</v>
@@ -1822,7 +1834,7 @@
         <v>294.4</v>
       </c>
       <c r="AB7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AC7">
         <v>89</v>
@@ -1834,7 +1846,7 @@
         <v>324.4</v>
       </c>
       <c r="AF7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG7">
         <v>99</v>
@@ -1846,7 +1858,7 @@
         <v>354.4</v>
       </c>
       <c r="AJ7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK7">
         <v>102</v>
@@ -1858,7 +1870,7 @@
         <v>363.4</v>
       </c>
       <c r="AN7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AO7">
         <v>109</v>
@@ -1870,7 +1882,7 @@
         <v>384.4</v>
       </c>
       <c r="AR7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AS7">
         <v>118</v>
@@ -1882,7 +1894,7 @@
         <v>411.4</v>
       </c>
       <c r="AV7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW7">
         <v>128</v>
@@ -1894,7 +1906,7 @@
         <v>441.4</v>
       </c>
       <c r="AZ7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BA7">
         <v>137</v>
@@ -1906,7 +1918,7 @@
         <v>468.4</v>
       </c>
       <c r="BD7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE7">
         <v>150</v>
@@ -1918,7 +1930,7 @@
         <v>507.4</v>
       </c>
       <c r="BH7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BI7">
         <v>147</v>
@@ -1928,6 +1940,170 @@
       </c>
       <c r="BK7">
         <v>498.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:63">
+      <c r="A8">
+        <v>294928</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8">
+        <v>147</v>
+      </c>
+      <c r="E8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" t="s">
+        <v>76</v>
+      </c>
+      <c r="T8" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>146</v>
+      </c>
+      <c r="W8">
+        <v>-275.9</v>
+      </c>
+      <c r="X8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8">
+        <v>8</v>
+      </c>
+      <c r="Z8">
+        <v>139</v>
+      </c>
+      <c r="AA8">
+        <v>-261.9</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC8">
+        <v>26</v>
+      </c>
+      <c r="AD8">
+        <v>121</v>
+      </c>
+      <c r="AE8">
+        <v>-225.9</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG8">
+        <v>44</v>
+      </c>
+      <c r="AH8">
+        <v>103</v>
+      </c>
+      <c r="AI8">
+        <v>-189.9</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK8">
+        <v>61</v>
+      </c>
+      <c r="AL8">
+        <v>86</v>
+      </c>
+      <c r="AM8">
+        <v>-155.9</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO8">
+        <v>77</v>
+      </c>
+      <c r="AP8">
+        <v>70</v>
+      </c>
+      <c r="AQ8">
+        <v>-123.9</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS8">
+        <v>92</v>
+      </c>
+      <c r="AT8">
+        <v>55</v>
+      </c>
+      <c r="AU8">
+        <v>-93.90000000000001</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW8">
+        <v>106</v>
+      </c>
+      <c r="AX8">
+        <v>41</v>
+      </c>
+      <c r="AY8">
+        <v>-65.90000000000001</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA8">
+        <v>119</v>
+      </c>
+      <c r="BB8">
+        <v>28</v>
+      </c>
+      <c r="BC8">
+        <v>-39.9</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE8">
+        <v>128</v>
+      </c>
+      <c r="BF8">
+        <v>19</v>
+      </c>
+      <c r="BG8">
+        <v>-21.9</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI8">
+        <v>132</v>
+      </c>
+      <c r="BJ8">
+        <v>15</v>
+      </c>
+      <c r="BK8">
+        <v>-13.9</v>
       </c>
     </row>
   </sheetData>
